--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N45_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.586783904714233</v>
+        <v>0.9078523845160629</v>
       </c>
       <c r="D2" t="n">
-        <v>5.703972689962431</v>
+        <v>0.9268955621188951</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
